--- a/tests/e2e/pliki/wniosek-z-ostrzezeniami.xlsx
+++ b/tests/e2e/pliki/wniosek-z-ostrzezeniami.xlsx
@@ -5316,14 +5316,13 @@
           <t>Uwagi, opis działalności, pytania do agenta</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+    </row>
+    <row r="37">
+      <c r="B37" s="38" t="inlineStr">
         <is>
           <t>Prosimy o wycenę wariantu z ochroną cyber.</t>
         </is>
       </c>
-    </row>
-    <row r="37">
-      <c r="B37" s="38" t="n"/>
       <c r="C37" s="39" t="n"/>
       <c r="D37" s="39" t="n"/>
       <c r="E37" s="39" t="n"/>
